--- a/AAII_Financials/Yearly/STTK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/STTK_YR_FIN.xlsx
@@ -772,10 +772,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>3000</v>
+        <v>35200</v>
       </c>
       <c r="E9" s="3">
-        <v>4900</v>
+        <v>67000</v>
       </c>
       <c r="F9" s="3">
         <v>74000</v>
@@ -817,10 +817,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-2000</v>
+        <v>-34200</v>
       </c>
       <c r="E10" s="3">
-        <v>800</v>
+        <v>-61300</v>
       </c>
       <c r="F10" s="3">
         <v>-72400</v>
@@ -881,10 +881,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>32200</v>
+        <v>35300</v>
       </c>
       <c r="E12" s="3">
-        <v>62100</v>
+        <v>67200</v>
       </c>
       <c r="F12" s="3">
         <v>74300</v>
